--- a/Unused File/template.xlsx
+++ b/Unused File/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\e-payslip\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\e-payslip\Unused File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087369FE-F46A-4340-9412-8DE222B030B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E414F54D-733D-4703-BB90-3514897A2677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E324F944-70B3-4EFA-82D2-B56BF41E8252}"/>
   </bookViews>
